--- a/xpts_playground.xlsx
+++ b/xpts_playground.xlsx
@@ -3,12 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet1!$A$1:$AW$424</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_9BC4FBD6_2D2B_40A0_8F60_4009531500E2_.wvu.FilterData">Sheet1!$A$1:$AW$424</definedName>
   </definedNames>
   <calcPr/>
+  <customWorkbookViews>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{9BC4FBD6-2D2B-40A0-8F60-4009531500E2}" name="Table1 filter view"/>
+  </customWorkbookViews>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="wo0TBAhA9t59iBAG8xui+3EBZKqmMNfnTFoFs2y7Bds="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2770,7 +2778,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2799,9 +2807,6 @@
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -2878,13 +2883,8 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AW424" displayName="Table1" name="Table1" id="1">
-  <autoFilter ref="$A$1:$AW$424"/>
   <tableColumns count="49">
     <tableColumn name="player_id" id="1"/>
     <tableColumn name="name" id="2"/>
@@ -3629,7 +3629,7 @@
       <c r="F4" s="6">
         <v>0.9375</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="5">
         <v>87.0</v>
       </c>
       <c r="H4" s="5">
@@ -4546,124 +4546,124 @@
         <v>0</v>
       </c>
       <c r="K10" s="7">
-        <v>0.0</v>
+        <v>73.02</v>
       </c>
       <c r="L10" s="8">
         <v>0.1238103691117823</v>
       </c>
       <c r="M10" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.857194396</v>
       </c>
       <c r="N10" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>131.1446095</v>
       </c>
       <c r="O10" s="9">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>16.39307618</v>
       </c>
       <c r="P10" s="9">
-        <v>0.0</v>
+        <v>4.492301156834015</v>
       </c>
       <c r="Q10" s="9">
-        <v>0.0</v>
+        <v>3.870714877603672</v>
       </c>
       <c r="R10" s="9">
-        <v>0.0</v>
+        <v>4.322435443171101</v>
       </c>
       <c r="S10" s="9">
-        <v>0.0</v>
+        <v>3.925675238423546</v>
       </c>
       <c r="T10" s="9">
-        <v>0.0</v>
+        <v>3.572586903497544</v>
       </c>
       <c r="U10" s="9">
-        <v>0.0</v>
+        <v>3.821854788044618</v>
       </c>
       <c r="V10" s="9">
-        <v>0.0</v>
+        <v>4.662044973117199</v>
       </c>
       <c r="W10" s="9">
-        <v>0.0</v>
+        <v>3.414748761198807</v>
       </c>
       <c r="X10" s="9">
-        <v>0.0</v>
+        <v>4.42099103529229</v>
       </c>
       <c r="Y10" s="9">
-        <v>0.0</v>
+        <v>3.917695383745312</v>
       </c>
       <c r="Z10" s="9">
-        <v>0.0</v>
+        <v>3.545906518379571</v>
       </c>
       <c r="AA10" s="9">
-        <v>0.0</v>
+        <v>3.419045235152576</v>
       </c>
       <c r="AB10" s="9">
-        <v>0.0</v>
+        <v>3.628465235976073</v>
       </c>
       <c r="AC10" s="9">
-        <v>0.0</v>
+        <v>3.507061574081828</v>
       </c>
       <c r="AD10" s="9">
-        <v>0.0</v>
+        <v>3.648503255357779</v>
       </c>
       <c r="AE10" s="9">
-        <v>0.0</v>
+        <v>3.326045773936452</v>
       </c>
       <c r="AF10" s="9">
-        <v>0.0</v>
+        <v>4.281799866571128</v>
       </c>
       <c r="AG10" s="9">
-        <v>0.0</v>
+        <v>4.401936931036844</v>
       </c>
       <c r="AH10" s="9">
-        <v>0.0</v>
+        <v>3.889746649457904</v>
       </c>
       <c r="AI10" s="9">
-        <v>0.0</v>
+        <v>4.466969824132929</v>
       </c>
       <c r="AJ10" s="9">
-        <v>0.0</v>
+        <v>3.4580375835121</v>
       </c>
       <c r="AK10" s="9">
-        <v>0.0</v>
+        <v>3.198752928474811</v>
       </c>
       <c r="AL10" s="9">
-        <v>0.0</v>
+        <v>4.171205636947835</v>
       </c>
       <c r="AM10" s="9">
-        <v>0.0</v>
+        <v>3.742013977526909</v>
       </c>
       <c r="AN10" s="9">
-        <v>0.0</v>
+        <v>3.8361703935185</v>
       </c>
       <c r="AO10" s="9">
-        <v>0.0</v>
+        <v>3.762124248124471</v>
       </c>
       <c r="AP10" s="9">
-        <v>0.0</v>
+        <v>3.860077860339972</v>
       </c>
       <c r="AQ10" s="9">
-        <v>0.0</v>
+        <v>4.017277467646146</v>
       </c>
       <c r="AR10" s="9">
-        <v>0.0</v>
+        <v>4.034649140876607</v>
       </c>
       <c r="AS10" s="9">
-        <v>0.0</v>
+        <v>3.149522864868257</v>
       </c>
       <c r="AT10" s="9">
-        <v>0.0</v>
+        <v>4.540122192496909</v>
       </c>
       <c r="AU10" s="9">
-        <v>0.0</v>
+        <v>3.731594191449535</v>
       </c>
       <c r="AV10" s="9">
-        <v>0.0</v>
+        <v>3.240735073191604</v>
       </c>
       <c r="AW10" s="9">
-        <v>0.0</v>
+        <v>3.86579647718753</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
@@ -5441,7 +5441,7 @@
       <c r="F16" s="6">
         <v>1.0</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="5">
         <v>85.0</v>
       </c>
       <c r="H16" s="5">
@@ -5593,7 +5593,7 @@
       <c r="F17" s="6">
         <v>0.8214285714</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="5">
         <v>75.0</v>
       </c>
       <c r="H17" s="5">
@@ -5897,7 +5897,7 @@
       <c r="F19" s="6">
         <v>1.0</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="5">
         <v>89.0</v>
       </c>
       <c r="H19" s="5">
@@ -6049,7 +6049,7 @@
       <c r="F20" s="6">
         <v>1.0</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="5">
         <v>85.0</v>
       </c>
       <c r="H20" s="5">
@@ -7561,7 +7561,7 @@
       <c r="F30" s="6">
         <v>0.8484848485</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="5">
         <v>79.0</v>
       </c>
       <c r="H30" s="5">
@@ -8317,7 +8317,7 @@
       <c r="F35" s="6">
         <v>0.5</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="5">
         <v>65.0</v>
       </c>
       <c r="H35" s="5">
@@ -9371,7 +9371,7 @@
         <v>6.0</v>
       </c>
       <c r="F42" s="6"/>
-      <c r="G42" s="10"/>
+      <c r="G42" s="5"/>
       <c r="H42" s="5">
         <v>1063.0</v>
       </c>
@@ -9825,7 +9825,7 @@
       <c r="F45" s="6">
         <v>0.7666666667</v>
       </c>
-      <c r="G45" s="10">
+      <c r="G45" s="5">
         <v>85.0</v>
       </c>
       <c r="H45" s="5">
@@ -10433,7 +10433,7 @@
       <c r="F49" s="6">
         <v>1.0</v>
       </c>
-      <c r="G49" s="10">
+      <c r="G49" s="5">
         <v>89.0</v>
       </c>
       <c r="H49" s="5">
@@ -10889,7 +10889,7 @@
       <c r="F52" s="6">
         <v>0.625</v>
       </c>
-      <c r="G52" s="10">
+      <c r="G52" s="5">
         <v>68.0</v>
       </c>
       <c r="H52" s="5">
@@ -13315,7 +13315,7 @@
       <c r="F68" s="6">
         <v>0.5333333333</v>
       </c>
-      <c r="G68" s="10">
+      <c r="G68" s="5">
         <v>80.0</v>
       </c>
       <c r="H68" s="5">
@@ -13617,7 +13617,7 @@
         <v>5.0</v>
       </c>
       <c r="F70" s="6"/>
-      <c r="G70" s="10"/>
+      <c r="G70" s="5"/>
       <c r="H70" s="5">
         <v>2563.0</v>
       </c>
@@ -14679,7 +14679,7 @@
       <c r="F77" s="6">
         <v>1.0</v>
       </c>
-      <c r="G77" s="10">
+      <c r="G77" s="5">
         <v>90.0</v>
       </c>
       <c r="H77" s="5">
@@ -15287,7 +15287,7 @@
       <c r="F81" s="6">
         <v>0.9032258065</v>
       </c>
-      <c r="G81" s="10">
+      <c r="G81" s="5">
         <v>79.0</v>
       </c>
       <c r="H81" s="5">
@@ -16199,7 +16199,7 @@
       <c r="F87" s="6">
         <v>0.92</v>
       </c>
-      <c r="G87" s="10">
+      <c r="G87" s="5">
         <v>79.0</v>
       </c>
       <c r="H87" s="5">
@@ -16499,7 +16499,7 @@
       <c r="F89" s="6">
         <v>0.3103448276</v>
       </c>
-      <c r="G89" s="10">
+      <c r="G89" s="5">
         <v>70.0</v>
       </c>
       <c r="H89" s="5">
@@ -16803,7 +16803,7 @@
       <c r="F91" s="6">
         <v>1.0</v>
       </c>
-      <c r="G91" s="10">
+      <c r="G91" s="5">
         <v>90.0</v>
       </c>
       <c r="H91" s="5">
@@ -17107,7 +17107,7 @@
       <c r="F93" s="6">
         <v>0.9285714286</v>
       </c>
-      <c r="G93" s="10">
+      <c r="G93" s="5">
         <v>86.0</v>
       </c>
       <c r="H93" s="5">
@@ -17411,7 +17411,7 @@
       <c r="F95" s="6">
         <v>0.9696969697</v>
       </c>
-      <c r="G95" s="10">
+      <c r="G95" s="5">
         <v>81.0</v>
       </c>
       <c r="H95" s="5">
@@ -18775,7 +18775,7 @@
       <c r="F104" s="6">
         <v>0.7647058824</v>
       </c>
-      <c r="G104" s="10">
+      <c r="G104" s="5">
         <v>84.0</v>
       </c>
       <c r="H104" s="5">
@@ -19231,7 +19231,7 @@
       <c r="F107" s="6">
         <v>0.8846153846</v>
       </c>
-      <c r="G107" s="10">
+      <c r="G107" s="5">
         <v>88.0</v>
       </c>
       <c r="H107" s="5">
@@ -19542,124 +19542,124 @@
         <v>0</v>
       </c>
       <c r="K109" s="7">
-        <v>0.0</v>
+        <v>23.98</v>
       </c>
       <c r="L109" s="8">
         <v>0.1477116861119041</v>
       </c>
       <c r="M109" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.140172304</v>
       </c>
       <c r="N109" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>72.76585832</v>
       </c>
       <c r="O109" s="9">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>12.12764305</v>
       </c>
       <c r="P109" s="9">
-        <v>0.0</v>
+        <v>2.143209968532872</v>
       </c>
       <c r="Q109" s="9">
-        <v>0.0</v>
+        <v>2.063587546942203</v>
       </c>
       <c r="R109" s="9">
-        <v>0.0</v>
+        <v>1.772360080579519</v>
       </c>
       <c r="S109" s="9">
-        <v>0.0</v>
+        <v>2.472607749853574</v>
       </c>
       <c r="T109" s="9">
-        <v>0.0</v>
+        <v>1.930372001300818</v>
       </c>
       <c r="U109" s="9">
-        <v>0.0</v>
+        <v>2.233083872087804</v>
       </c>
       <c r="V109" s="9">
-        <v>0.0</v>
+        <v>2.54328844781165</v>
       </c>
       <c r="W109" s="9">
-        <v>0.0</v>
+        <v>2.081701076308644</v>
       </c>
       <c r="X109" s="9">
-        <v>0.0</v>
+        <v>2.139817104402072</v>
       </c>
       <c r="Y109" s="9">
-        <v>0.0</v>
+        <v>1.931420129040503</v>
       </c>
       <c r="Z109" s="9">
-        <v>0.0</v>
+        <v>2.324409690596938</v>
       </c>
       <c r="AA109" s="9">
-        <v>0.0</v>
+        <v>1.822975049941242</v>
       </c>
       <c r="AB109" s="9">
-        <v>0.0</v>
+        <v>2.24339051241129</v>
       </c>
       <c r="AC109" s="9">
-        <v>0.0</v>
+        <v>2.499887035665778</v>
       </c>
       <c r="AD109" s="9">
-        <v>0.0</v>
+        <v>2.157419642408352</v>
       </c>
       <c r="AE109" s="9">
-        <v>0.0</v>
+        <v>1.969248279561767</v>
       </c>
       <c r="AF109" s="9">
-        <v>0.0</v>
+        <v>2.117139297090109</v>
       </c>
       <c r="AG109" s="9">
-        <v>0.0</v>
+        <v>2.615625420216189</v>
       </c>
       <c r="AH109" s="9">
-        <v>0.0</v>
+        <v>1.875602668087356</v>
       </c>
       <c r="AI109" s="9">
-        <v>0.0</v>
+        <v>2.014289567347597</v>
       </c>
       <c r="AJ109" s="9">
-        <v>0.0</v>
+        <v>2.214110275041343</v>
       </c>
       <c r="AK109" s="9">
-        <v>0.0</v>
+        <v>2.069769621974494</v>
       </c>
       <c r="AL109" s="9">
-        <v>0.0</v>
+        <v>2.178736129247967</v>
       </c>
       <c r="AM109" s="9">
-        <v>0.0</v>
+        <v>2.146128063029789</v>
       </c>
       <c r="AN109" s="9">
-        <v>0.0</v>
+        <v>2.514916154139342</v>
       </c>
       <c r="AO109" s="9">
-        <v>0.0</v>
+        <v>1.878151772661985</v>
       </c>
       <c r="AP109" s="9">
-        <v>0.0</v>
+        <v>2.002400979770429</v>
       </c>
       <c r="AQ109" s="9">
-        <v>0.0</v>
+        <v>1.953418766223878</v>
       </c>
       <c r="AR109" s="9">
-        <v>0.0</v>
+        <v>2.414134566160477</v>
       </c>
       <c r="AS109" s="9">
-        <v>0.0</v>
+        <v>2.125632767734807</v>
       </c>
       <c r="AT109" s="9">
-        <v>0.0</v>
+        <v>2.390025416351064</v>
       </c>
       <c r="AU109" s="9">
-        <v>0.0</v>
+        <v>1.718243737736326</v>
       </c>
       <c r="AV109" s="9">
-        <v>0.0</v>
+        <v>2.461302920627181</v>
       </c>
       <c r="AW109" s="9">
-        <v>0.0</v>
+        <v>1.747452009844815</v>
       </c>
     </row>
     <row r="110" ht="15.0" customHeight="1">
@@ -22109,7 +22109,7 @@
       <c r="F126" s="6">
         <v>0.9411764706</v>
       </c>
-      <c r="G126" s="10">
+      <c r="G126" s="5">
         <v>86.0</v>
       </c>
       <c r="H126" s="5">
@@ -22409,7 +22409,7 @@
       <c r="F128" s="6">
         <v>0.6896551724</v>
       </c>
-      <c r="G128" s="10">
+      <c r="G128" s="5">
         <v>82.0</v>
       </c>
       <c r="H128" s="5">
@@ -22559,7 +22559,7 @@
         <v>5.0</v>
       </c>
       <c r="F129" s="6"/>
-      <c r="G129" s="10"/>
+      <c r="G129" s="5"/>
       <c r="H129" s="5">
         <v>3228.0</v>
       </c>
@@ -23165,7 +23165,7 @@
       <c r="F133" s="6">
         <v>0.8571428571</v>
       </c>
-      <c r="G133" s="10">
+      <c r="G133" s="5">
         <v>73.0</v>
       </c>
       <c r="H133" s="5">
@@ -24529,7 +24529,7 @@
       <c r="F142" s="6">
         <v>0.9375</v>
       </c>
-      <c r="G142" s="10">
+      <c r="G142" s="5">
         <v>84.0</v>
       </c>
       <c r="H142" s="5">
@@ -24681,7 +24681,7 @@
       <c r="F143" s="6">
         <v>0.303030303</v>
       </c>
-      <c r="G143" s="10">
+      <c r="G143" s="5">
         <v>90.0</v>
       </c>
       <c r="H143" s="5">
@@ -25137,7 +25137,7 @@
       <c r="F146" s="6">
         <v>0.96875</v>
       </c>
-      <c r="G146" s="10">
+      <c r="G146" s="5">
         <v>90.0</v>
       </c>
       <c r="H146" s="5">
@@ -25593,7 +25593,7 @@
       <c r="F149" s="6">
         <v>1.0</v>
       </c>
-      <c r="G149" s="10">
+      <c r="G149" s="5">
         <v>85.0</v>
       </c>
       <c r="H149" s="5">
@@ -28465,7 +28465,7 @@
       <c r="F168" s="6">
         <v>0.6</v>
       </c>
-      <c r="G168" s="10">
+      <c r="G168" s="5">
         <v>84.0</v>
       </c>
       <c r="H168" s="5">
@@ -28769,7 +28769,7 @@
       <c r="F170" s="6">
         <v>0.0</v>
       </c>
-      <c r="G170" s="10"/>
+      <c r="G170" s="5"/>
       <c r="H170" s="5">
         <v>933.0</v>
       </c>
@@ -29071,7 +29071,7 @@
       <c r="F172" s="6">
         <v>0.303030303</v>
       </c>
-      <c r="G172" s="10">
+      <c r="G172" s="5">
         <v>71.0</v>
       </c>
       <c r="H172" s="5">
@@ -29373,7 +29373,7 @@
         <v>4.5</v>
       </c>
       <c r="F174" s="6"/>
-      <c r="G174" s="10"/>
+      <c r="G174" s="5"/>
       <c r="H174" s="5">
         <v>1430.0</v>
       </c>
@@ -29523,7 +29523,7 @@
       <c r="F175" s="6">
         <v>0.9</v>
       </c>
-      <c r="G175" s="10">
+      <c r="G175" s="5">
         <v>86.0</v>
       </c>
       <c r="H175" s="5">
@@ -29979,7 +29979,7 @@
       <c r="F178" s="6">
         <v>1.0</v>
       </c>
-      <c r="G178" s="10">
+      <c r="G178" s="5">
         <v>89.0</v>
       </c>
       <c r="H178" s="5">
@@ -31791,7 +31791,7 @@
       <c r="F190" s="6">
         <v>0.28</v>
       </c>
-      <c r="G190" s="10">
+      <c r="G190" s="5">
         <v>80.0</v>
       </c>
       <c r="H190" s="5">
@@ -34669,7 +34669,7 @@
         <v>4.0</v>
       </c>
       <c r="F209" s="6"/>
-      <c r="G209" s="10"/>
+      <c r="G209" s="5"/>
       <c r="H209" s="5">
         <v>1537.0</v>
       </c>
@@ -35263,7 +35263,7 @@
       <c r="F213" s="6">
         <v>0.2068965517</v>
       </c>
-      <c r="G213" s="10">
+      <c r="G213" s="5">
         <v>67.0</v>
       </c>
       <c r="H213" s="5">
@@ -35426,124 +35426,124 @@
         <v>0</v>
       </c>
       <c r="K214" s="7">
-        <v>0.0</v>
+        <v>22.95</v>
       </c>
       <c r="L214" s="8">
         <v>0.08586048246215958</v>
       </c>
       <c r="M214" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.866080562</v>
       </c>
       <c r="N214" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>63.44673909</v>
       </c>
       <c r="O214" s="9">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.930842387</v>
       </c>
       <c r="P214" s="9">
-        <v>0.0</v>
+        <v>1.893053731882652</v>
       </c>
       <c r="Q214" s="9">
-        <v>0.0</v>
+        <v>1.94043936432435</v>
       </c>
       <c r="R214" s="9">
         <v>0.0</v>
       </c>
       <c r="S214" s="9">
-        <v>0.0</v>
+        <v>1.877430735251802</v>
       </c>
       <c r="T214" s="9">
-        <v>0.0</v>
+        <v>1.76381651437511</v>
       </c>
       <c r="U214" s="9">
-        <v>0.0</v>
+        <v>3.982561312960118</v>
       </c>
       <c r="V214" s="9">
-        <v>0.0</v>
+        <v>2.065578830153391</v>
       </c>
       <c r="W214" s="9">
-        <v>0.0</v>
+        <v>1.918979681346428</v>
       </c>
       <c r="X214" s="9">
-        <v>0.0</v>
+        <v>1.689708659964392</v>
       </c>
       <c r="Y214" s="9">
-        <v>0.0</v>
+        <v>1.772529740201726</v>
       </c>
       <c r="Z214" s="9">
-        <v>0.0</v>
+        <v>1.813191445530418</v>
       </c>
       <c r="AA214" s="9">
-        <v>0.0</v>
+        <v>1.555555759761448</v>
       </c>
       <c r="AB214" s="9">
-        <v>0.0</v>
+        <v>2.04790907204179</v>
       </c>
       <c r="AC214" s="9">
-        <v>0.0</v>
+        <v>1.576962698915035</v>
       </c>
       <c r="AD214" s="9">
-        <v>0.0</v>
+        <v>1.867016369659929</v>
       </c>
       <c r="AE214" s="9">
-        <v>0.0</v>
+        <v>2.100148834510139</v>
       </c>
       <c r="AF214" s="9">
-        <v>0.0</v>
+        <v>1.932885558283949</v>
       </c>
       <c r="AG214" s="9">
-        <v>0.0</v>
+        <v>1.869155060750861</v>
       </c>
       <c r="AH214" s="9">
-        <v>0.0</v>
+        <v>1.889583814294963</v>
       </c>
       <c r="AI214" s="9">
-        <v>0.0</v>
+        <v>2.139442334083101</v>
       </c>
       <c r="AJ214" s="9">
-        <v>0.0</v>
+        <v>1.727917120494352</v>
       </c>
       <c r="AK214" s="9">
-        <v>0.0</v>
+        <v>1.821936088691652</v>
       </c>
       <c r="AL214" s="9">
-        <v>0.0</v>
+        <v>2.21325283280421</v>
       </c>
       <c r="AM214" s="9">
-        <v>0.0</v>
+        <v>1.73951867732717</v>
       </c>
       <c r="AN214" s="9">
-        <v>0.0</v>
+        <v>1.808660561143707</v>
       </c>
       <c r="AO214" s="9">
-        <v>0.0</v>
+        <v>2.160236579016003</v>
       </c>
       <c r="AP214" s="9">
-        <v>0.0</v>
+        <v>1.711794171286772</v>
       </c>
       <c r="AQ214" s="9">
-        <v>0.0</v>
+        <v>1.711025991414121</v>
       </c>
       <c r="AR214" s="9">
-        <v>0.0</v>
+        <v>1.672753434485532</v>
       </c>
       <c r="AS214" s="9">
-        <v>0.0</v>
+        <v>1.59521799154825</v>
       </c>
       <c r="AT214" s="9">
-        <v>0.0</v>
+        <v>2.108434219913706</v>
       </c>
       <c r="AU214" s="9">
-        <v>0.0</v>
+        <v>1.632314043151801</v>
       </c>
       <c r="AV214" s="9">
-        <v>0.0</v>
+        <v>1.999818865146985</v>
       </c>
       <c r="AW214" s="9">
-        <v>0.0</v>
+        <v>1.847908999145321</v>
       </c>
     </row>
     <row r="215" ht="15.0" customHeight="1">
@@ -37065,7 +37065,7 @@
       <c r="F225" s="6">
         <v>0.1515151515</v>
       </c>
-      <c r="G225" s="10">
+      <c r="G225" s="5">
         <v>59.0</v>
       </c>
       <c r="H225" s="5">
@@ -38571,7 +38571,7 @@
         <v>4.5</v>
       </c>
       <c r="F235" s="6"/>
-      <c r="G235" s="10"/>
+      <c r="G235" s="5"/>
       <c r="H235" s="5">
         <v>964.0</v>
       </c>
@@ -38867,7 +38867,7 @@
         <v>4.5</v>
       </c>
       <c r="F237" s="6"/>
-      <c r="G237" s="10"/>
+      <c r="G237" s="5"/>
       <c r="H237" s="5">
         <v>1211.0</v>
       </c>
@@ -39017,7 +39017,7 @@
       <c r="F238" s="6">
         <v>0.2272727273</v>
       </c>
-      <c r="G238" s="10">
+      <c r="G238" s="5">
         <v>64.0</v>
       </c>
       <c r="H238" s="5">
@@ -39319,7 +39319,7 @@
         <v>5.0</v>
       </c>
       <c r="F240" s="6"/>
-      <c r="G240" s="10"/>
+      <c r="G240" s="5"/>
       <c r="H240" s="5">
         <v>2096.0</v>
       </c>
@@ -39619,7 +39619,7 @@
         <v>4.5</v>
       </c>
       <c r="F242" s="6"/>
-      <c r="G242" s="10"/>
+      <c r="G242" s="5"/>
       <c r="H242" s="5">
         <v>2968.0</v>
       </c>
@@ -39917,7 +39917,7 @@
       <c r="F244" s="6">
         <v>0.0</v>
       </c>
-      <c r="G244" s="10"/>
+      <c r="G244" s="5"/>
       <c r="H244" s="5">
         <v>90.0</v>
       </c>
@@ -40515,7 +40515,7 @@
       <c r="F248" s="6">
         <v>0.5555555556</v>
       </c>
-      <c r="G248" s="10">
+      <c r="G248" s="5">
         <v>80.0</v>
       </c>
       <c r="H248" s="5">
@@ -40667,7 +40667,7 @@
       <c r="F249" s="6">
         <v>0.2857142857</v>
       </c>
-      <c r="G249" s="10">
+      <c r="G249" s="5">
         <v>53.0</v>
       </c>
       <c r="H249" s="5">
@@ -40819,7 +40819,7 @@
       <c r="F250" s="6">
         <v>0.0</v>
       </c>
-      <c r="G250" s="10"/>
+      <c r="G250" s="5"/>
       <c r="H250" s="5">
         <v>382.0</v>
       </c>
@@ -41565,7 +41565,7 @@
         <v>4.5</v>
       </c>
       <c r="F255" s="6"/>
-      <c r="G255" s="10"/>
+      <c r="G255" s="5"/>
       <c r="H255" s="5">
         <v>1900.0</v>
       </c>
@@ -43219,7 +43219,7 @@
       <c r="F266" s="6">
         <v>0.347826087</v>
       </c>
-      <c r="G266" s="10">
+      <c r="G266" s="5">
         <v>75.0</v>
       </c>
       <c r="H266" s="5">
@@ -43671,7 +43671,7 @@
       <c r="F269" s="6">
         <v>0.2222222222</v>
       </c>
-      <c r="G269" s="10">
+      <c r="G269" s="5">
         <v>72.0</v>
       </c>
       <c r="H269" s="5">
@@ -43969,7 +43969,7 @@
         <v>5.0</v>
       </c>
       <c r="F271" s="6"/>
-      <c r="G271" s="10"/>
+      <c r="G271" s="5"/>
       <c r="H271" s="5">
         <v>1460.0</v>
       </c>
@@ -44419,7 +44419,7 @@
       <c r="F274" s="6">
         <v>0.8275862069</v>
       </c>
-      <c r="G274" s="10">
+      <c r="G274" s="5">
         <v>80.0</v>
       </c>
       <c r="H274" s="5">
@@ -44865,7 +44865,7 @@
         <v>4.5</v>
       </c>
       <c r="F277" s="6"/>
-      <c r="G277" s="10"/>
+      <c r="G277" s="5"/>
       <c r="H277" s="5">
         <v>1193.0</v>
       </c>
@@ -45457,7 +45457,7 @@
         <v>4.5</v>
       </c>
       <c r="F281" s="6"/>
-      <c r="G281" s="10"/>
+      <c r="G281" s="5"/>
       <c r="H281" s="5">
         <v>3310.0</v>
       </c>
@@ -45911,7 +45911,7 @@
       <c r="F284" s="6">
         <v>0.2222222222</v>
       </c>
-      <c r="G284" s="10">
+      <c r="G284" s="5">
         <v>80.0</v>
       </c>
       <c r="H284" s="5">
@@ -46667,7 +46667,7 @@
       <c r="F289" s="6">
         <v>0.06896551724</v>
       </c>
-      <c r="G289" s="10">
+      <c r="G289" s="5">
         <v>56.0</v>
       </c>
       <c r="H289" s="5">
@@ -46971,7 +46971,7 @@
       <c r="F291" s="6">
         <v>0.1724137931</v>
       </c>
-      <c r="G291" s="10">
+      <c r="G291" s="5">
         <v>73.0</v>
       </c>
       <c r="H291" s="5">
@@ -47121,7 +47121,7 @@
         <v>6.0</v>
       </c>
       <c r="F292" s="6"/>
-      <c r="G292" s="10"/>
+      <c r="G292" s="5"/>
       <c r="H292" s="5">
         <v>1473.0</v>
       </c>
@@ -47271,7 +47271,7 @@
       <c r="F293" s="6">
         <v>0.4333333333</v>
       </c>
-      <c r="G293" s="10">
+      <c r="G293" s="5">
         <v>75.0</v>
       </c>
       <c r="H293" s="5">
@@ -47423,7 +47423,7 @@
       <c r="F294" s="6">
         <v>0.2307692308</v>
       </c>
-      <c r="G294" s="10">
+      <c r="G294" s="5">
         <v>63.0</v>
       </c>
       <c r="H294" s="5">
@@ -47871,7 +47871,7 @@
       <c r="F297" s="6">
         <v>0.07142857143</v>
       </c>
-      <c r="G297" s="10">
+      <c r="G297" s="5">
         <v>67.0</v>
       </c>
       <c r="H297" s="5">
@@ -48021,7 +48021,7 @@
         <v>4.5</v>
       </c>
       <c r="F298" s="6"/>
-      <c r="G298" s="10"/>
+      <c r="G298" s="5"/>
       <c r="H298" s="5">
         <v>494.0</v>
       </c>
@@ -48169,7 +48169,7 @@
         <v>6.0</v>
       </c>
       <c r="F299" s="6"/>
-      <c r="G299" s="10"/>
+      <c r="G299" s="5"/>
       <c r="H299" s="5">
         <v>2955.0</v>
       </c>
@@ -48317,7 +48317,7 @@
         <v>7.0</v>
       </c>
       <c r="F300" s="6"/>
-      <c r="G300" s="10"/>
+      <c r="G300" s="5"/>
       <c r="H300" s="5">
         <v>1150.0</v>
       </c>
@@ -49379,7 +49379,7 @@
       <c r="F307" s="6">
         <v>0.03846153846</v>
       </c>
-      <c r="G307" s="10">
+      <c r="G307" s="5">
         <v>57.0</v>
       </c>
       <c r="H307" s="5">
@@ -49681,7 +49681,7 @@
         <v>5.5</v>
       </c>
       <c r="F309" s="6"/>
-      <c r="G309" s="10"/>
+      <c r="G309" s="5"/>
       <c r="H309" s="5">
         <v>2645.0</v>
       </c>
@@ -49829,7 +49829,7 @@
         <v>5.0</v>
       </c>
       <c r="F310" s="6"/>
-      <c r="G310" s="10"/>
+      <c r="G310" s="5"/>
       <c r="H310" s="5">
         <v>1737.0</v>
       </c>
@@ -50577,7 +50577,7 @@
         <v>4.0</v>
       </c>
       <c r="F315" s="6"/>
-      <c r="G315" s="10"/>
+      <c r="G315" s="5"/>
       <c r="H315" s="5">
         <v>2830.0</v>
       </c>
@@ -51025,7 +51025,7 @@
         <v>4.5</v>
       </c>
       <c r="F318" s="6"/>
-      <c r="G318" s="10"/>
+      <c r="G318" s="5"/>
       <c r="H318" s="5">
         <v>1313.0</v>
       </c>
@@ -51175,7 +51175,7 @@
       <c r="F319" s="6">
         <v>1.0</v>
       </c>
-      <c r="G319" s="10">
+      <c r="G319" s="5">
         <v>56.0</v>
       </c>
       <c r="H319" s="5">
@@ -51783,7 +51783,7 @@
       <c r="F323" s="6">
         <v>0.03125</v>
       </c>
-      <c r="G323" s="10">
+      <c r="G323" s="5">
         <v>90.0</v>
       </c>
       <c r="H323" s="5">
@@ -51933,7 +51933,7 @@
         <v>5.0</v>
       </c>
       <c r="F324" s="6"/>
-      <c r="G324" s="10"/>
+      <c r="G324" s="5"/>
       <c r="H324" s="5">
         <v>2313.0</v>
       </c>
@@ -52233,7 +52233,7 @@
         <v>5.0</v>
       </c>
       <c r="F326" s="6"/>
-      <c r="G326" s="10"/>
+      <c r="G326" s="5"/>
       <c r="H326" s="5">
         <v>363.0</v>
       </c>
@@ -52383,7 +52383,7 @@
       <c r="F327" s="6">
         <v>0.2941176471</v>
       </c>
-      <c r="G327" s="10">
+      <c r="G327" s="5">
         <v>66.0</v>
       </c>
       <c r="H327" s="5">
@@ -52533,7 +52533,7 @@
         <v>4.5</v>
       </c>
       <c r="F328" s="6"/>
-      <c r="G328" s="10"/>
+      <c r="G328" s="5"/>
       <c r="H328" s="5">
         <v>3307.0</v>
       </c>
@@ -52683,7 +52683,7 @@
       <c r="F329" s="6">
         <v>0.1538461538</v>
       </c>
-      <c r="G329" s="10">
+      <c r="G329" s="5">
         <v>78.0</v>
       </c>
       <c r="H329" s="5">
@@ -52833,7 +52833,7 @@
         <v>4.5</v>
       </c>
       <c r="F330" s="6"/>
-      <c r="G330" s="10"/>
+      <c r="G330" s="5"/>
       <c r="H330" s="5">
         <v>2265.0</v>
       </c>
@@ -53131,7 +53131,7 @@
       <c r="F332" s="6">
         <v>0.2307692308</v>
       </c>
-      <c r="G332" s="10">
+      <c r="G332" s="5">
         <v>80.0</v>
       </c>
       <c r="H332" s="5">
@@ -53435,7 +53435,7 @@
       <c r="F334" s="6">
         <v>0.2727272727</v>
       </c>
-      <c r="G334" s="10">
+      <c r="G334" s="5">
         <v>80.0</v>
       </c>
       <c r="H334" s="5">
@@ -53739,7 +53739,7 @@
       <c r="F336" s="6">
         <v>0.4242424242</v>
       </c>
-      <c r="G336" s="10">
+      <c r="G336" s="5">
         <v>78.0</v>
       </c>
       <c r="H336" s="5">
@@ -53891,7 +53891,7 @@
       <c r="F337" s="6">
         <v>0.0</v>
       </c>
-      <c r="G337" s="10"/>
+      <c r="G337" s="5"/>
       <c r="H337" s="5">
         <v>273.0</v>
       </c>
@@ -54039,7 +54039,7 @@
         <v>5.5</v>
       </c>
       <c r="F338" s="6"/>
-      <c r="G338" s="10"/>
+      <c r="G338" s="5"/>
       <c r="H338" s="5">
         <v>503.0</v>
       </c>
@@ -54339,7 +54339,7 @@
       <c r="F340" s="6">
         <v>0.625</v>
       </c>
-      <c r="G340" s="10">
+      <c r="G340" s="5">
         <v>64.0</v>
       </c>
       <c r="H340" s="5">
@@ -54489,7 +54489,7 @@
         <v>4.5</v>
       </c>
       <c r="F341" s="6"/>
-      <c r="G341" s="10"/>
+      <c r="G341" s="5"/>
       <c r="H341" s="5">
         <v>1906.0</v>
       </c>
@@ -54785,7 +54785,7 @@
         <v>5.0</v>
       </c>
       <c r="F343" s="6"/>
-      <c r="G343" s="10"/>
+      <c r="G343" s="5"/>
       <c r="H343" s="5">
         <v>91.0</v>
       </c>
@@ -54935,7 +54935,7 @@
       <c r="F344" s="6">
         <v>0.0</v>
       </c>
-      <c r="G344" s="10"/>
+      <c r="G344" s="5"/>
       <c r="H344" s="5">
         <v>245.0</v>
       </c>
@@ -55235,7 +55235,7 @@
         <v>4.5</v>
       </c>
       <c r="F346" s="6"/>
-      <c r="G346" s="10"/>
+      <c r="G346" s="5"/>
       <c r="H346" s="5">
         <v>3263.0</v>
       </c>
@@ -55385,7 +55385,7 @@
       <c r="F347" s="6">
         <v>0.1851851852</v>
       </c>
-      <c r="G347" s="10">
+      <c r="G347" s="5">
         <v>76.0</v>
       </c>
       <c r="H347" s="5">
@@ -55537,7 +55537,7 @@
       <c r="F348" s="6">
         <v>0.3</v>
       </c>
-      <c r="G348" s="10">
+      <c r="G348" s="5">
         <v>72.0</v>
       </c>
       <c r="H348" s="5">
@@ -56135,7 +56135,7 @@
         <v>4.0</v>
       </c>
       <c r="F352" s="6"/>
-      <c r="G352" s="10"/>
+      <c r="G352" s="5"/>
       <c r="H352" s="5">
         <v>1330.0</v>
       </c>
@@ -56735,7 +56735,7 @@
         <v>5.5</v>
       </c>
       <c r="F356" s="6"/>
-      <c r="G356" s="10"/>
+      <c r="G356" s="5"/>
       <c r="H356" s="5">
         <v>1674.0</v>
       </c>
@@ -57183,7 +57183,7 @@
         <v>4.5</v>
       </c>
       <c r="F359" s="6"/>
-      <c r="G359" s="10"/>
+      <c r="G359" s="5"/>
       <c r="H359" s="5">
         <v>3460.0</v>
       </c>
@@ -57333,7 +57333,7 @@
       <c r="F360" s="6">
         <v>0.7741935484</v>
       </c>
-      <c r="G360" s="10">
+      <c r="G360" s="5">
         <v>82.0</v>
       </c>
       <c r="H360" s="5">
@@ -57485,7 +57485,7 @@
       <c r="F361" s="6">
         <v>0.9166666667</v>
       </c>
-      <c r="G361" s="10">
+      <c r="G361" s="5">
         <v>81.0</v>
       </c>
       <c r="H361" s="5">
@@ -57789,7 +57789,7 @@
       <c r="F363" s="6">
         <v>0.9189189189</v>
       </c>
-      <c r="G363" s="10">
+      <c r="G363" s="5">
         <v>86.0</v>
       </c>
       <c r="H363" s="5">
@@ -57941,7 +57941,7 @@
       <c r="F364" s="6">
         <v>0.5185185185</v>
       </c>
-      <c r="G364" s="10">
+      <c r="G364" s="5">
         <v>72.0</v>
       </c>
       <c r="H364" s="5">
@@ -58091,7 +58091,7 @@
         <v>4.0</v>
       </c>
       <c r="F365" s="6"/>
-      <c r="G365" s="10"/>
+      <c r="G365" s="5"/>
       <c r="H365" s="5">
         <v>3193.0</v>
       </c>
@@ -58241,7 +58241,7 @@
       <c r="F366" s="6">
         <v>0.1818181818</v>
       </c>
-      <c r="G366" s="10">
+      <c r="G366" s="5">
         <v>60.0</v>
       </c>
       <c r="H366" s="5">
@@ -59605,7 +59605,7 @@
       <c r="F375" s="6">
         <v>0.3611111111</v>
       </c>
-      <c r="G375" s="10">
+      <c r="G375" s="5">
         <v>62.0</v>
       </c>
       <c r="H375" s="5">
@@ -59757,7 +59757,7 @@
       <c r="F376" s="6">
         <v>0.6756756757</v>
       </c>
-      <c r="G376" s="10">
+      <c r="G376" s="5">
         <v>70.0</v>
       </c>
       <c r="H376" s="5">
@@ -60205,7 +60205,7 @@
       <c r="F379" s="6">
         <v>1.0</v>
       </c>
-      <c r="G379" s="10">
+      <c r="G379" s="5">
         <v>90.0</v>
       </c>
       <c r="H379" s="5">
@@ -60963,7 +60963,7 @@
         <v>4.0</v>
       </c>
       <c r="F384" s="6"/>
-      <c r="G384" s="10"/>
+      <c r="G384" s="5"/>
       <c r="H384" s="5">
         <v>1852.0</v>
       </c>
@@ -61413,7 +61413,7 @@
       <c r="F387" s="6">
         <v>0.4375</v>
       </c>
-      <c r="G387" s="10">
+      <c r="G387" s="5">
         <v>56.0</v>
       </c>
       <c r="H387" s="5">
@@ -63073,7 +63073,7 @@
       <c r="F398" s="6">
         <v>0.7</v>
       </c>
-      <c r="G398" s="10">
+      <c r="G398" s="5">
         <v>81.0</v>
       </c>
       <c r="H398" s="5">
@@ -63225,7 +63225,7 @@
       <c r="F399" s="6">
         <v>0.7142857143</v>
       </c>
-      <c r="G399" s="10">
+      <c r="G399" s="5">
         <v>89.0</v>
       </c>
       <c r="H399" s="5">
@@ -63377,7 +63377,7 @@
       <c r="F400" s="6">
         <v>1.0</v>
       </c>
-      <c r="G400" s="10">
+      <c r="G400" s="5">
         <v>77.0</v>
       </c>
       <c r="H400" s="5">
@@ -63681,7 +63681,7 @@
       <c r="F402" s="6">
         <v>0.1176470588</v>
       </c>
-      <c r="G402" s="10">
+      <c r="G402" s="5">
         <v>68.0</v>
       </c>
       <c r="H402" s="5">
@@ -63833,7 +63833,7 @@
       <c r="F403" s="6">
         <v>0.2142857143</v>
       </c>
-      <c r="G403" s="10">
+      <c r="G403" s="5">
         <v>86.0</v>
       </c>
       <c r="H403" s="5">
@@ -63985,7 +63985,7 @@
       <c r="F404" s="6">
         <v>0.9090909091</v>
       </c>
-      <c r="G404" s="10">
+      <c r="G404" s="5">
         <v>89.0</v>
       </c>
       <c r="H404" s="5">
@@ -64137,7 +64137,7 @@
       <c r="F405" s="6">
         <v>0.25</v>
       </c>
-      <c r="G405" s="10">
+      <c r="G405" s="5">
         <v>80.0</v>
       </c>
       <c r="H405" s="5">
@@ -64289,7 +64289,7 @@
       <c r="F406" s="6">
         <v>0.875</v>
       </c>
-      <c r="G406" s="10">
+      <c r="G406" s="5">
         <v>81.0</v>
       </c>
       <c r="H406" s="5">
@@ -64441,7 +64441,7 @@
       <c r="F407" s="6">
         <v>0.3214285714</v>
       </c>
-      <c r="G407" s="10">
+      <c r="G407" s="5">
         <v>72.0</v>
       </c>
       <c r="H407" s="5">
@@ -64593,7 +64593,7 @@
       <c r="F408" s="6">
         <v>0.6216216216</v>
       </c>
-      <c r="G408" s="10">
+      <c r="G408" s="5">
         <v>82.0</v>
       </c>
       <c r="H408" s="5">
@@ -64895,7 +64895,7 @@
         <v>6.0</v>
       </c>
       <c r="F410" s="6"/>
-      <c r="G410" s="10"/>
+      <c r="G410" s="5"/>
       <c r="H410" s="5">
         <v>918.0</v>
       </c>
@@ -65045,7 +65045,7 @@
       <c r="F411" s="6">
         <v>1.0</v>
       </c>
-      <c r="G411" s="10">
+      <c r="G411" s="5">
         <v>88.0</v>
       </c>
       <c r="H411" s="5">
@@ -65197,7 +65197,7 @@
       <c r="F412" s="6">
         <v>0.6206896552</v>
       </c>
-      <c r="G412" s="10">
+      <c r="G412" s="5">
         <v>73.0</v>
       </c>
       <c r="H412" s="5">
@@ -65349,7 +65349,7 @@
       <c r="F413" s="6">
         <v>0.08108108108</v>
       </c>
-      <c r="G413" s="10">
+      <c r="G413" s="5">
         <v>73.0</v>
       </c>
       <c r="H413" s="5">
@@ -65499,7 +65499,7 @@
         <v>6.0</v>
       </c>
       <c r="F414" s="6"/>
-      <c r="G414" s="10"/>
+      <c r="G414" s="5"/>
       <c r="H414" s="5">
         <v>988.0</v>
       </c>
@@ -65647,7 +65647,7 @@
         <v>5.0</v>
       </c>
       <c r="F415" s="6"/>
-      <c r="G415" s="10"/>
+      <c r="G415" s="5"/>
       <c r="H415" s="5">
         <v>1703.0</v>
       </c>
@@ -65795,7 +65795,7 @@
         <v>7.0</v>
       </c>
       <c r="F416" s="6"/>
-      <c r="G416" s="10"/>
+      <c r="G416" s="5"/>
       <c r="H416" s="5">
         <v>548.0</v>
       </c>
@@ -65943,7 +65943,7 @@
         <v>8.5</v>
       </c>
       <c r="F417" s="6"/>
-      <c r="G417" s="10"/>
+      <c r="G417" s="5"/>
       <c r="H417" s="5">
         <v>2413.0</v>
       </c>
@@ -66091,7 +66091,7 @@
         <v>5.5</v>
       </c>
       <c r="F418" s="6"/>
-      <c r="G418" s="10"/>
+      <c r="G418" s="5"/>
       <c r="H418" s="5">
         <v>1295.0</v>
       </c>
@@ -66239,7 +66239,7 @@
         <v>5.5</v>
       </c>
       <c r="F419" s="6"/>
-      <c r="G419" s="10"/>
+      <c r="G419" s="5"/>
       <c r="H419" s="5">
         <v>3143.0</v>
       </c>
@@ -66387,7 +66387,7 @@
         <v>8.5</v>
       </c>
       <c r="F420" s="6"/>
-      <c r="G420" s="10"/>
+      <c r="G420" s="5"/>
       <c r="H420" s="5">
         <v>3286.0</v>
       </c>
@@ -66535,7 +66535,7 @@
         <v>5.5</v>
       </c>
       <c r="F421" s="6"/>
-      <c r="G421" s="10"/>
+      <c r="G421" s="5"/>
       <c r="H421" s="5">
         <v>646.0</v>
       </c>
@@ -66683,7 +66683,7 @@
         <v>5.0</v>
       </c>
       <c r="F422" s="6"/>
-      <c r="G422" s="10"/>
+      <c r="G422" s="5"/>
       <c r="H422" s="5">
         <v>766.0</v>
       </c>
@@ -66831,7 +66831,7 @@
         <v>4.5</v>
       </c>
       <c r="F423" s="6"/>
-      <c r="G423" s="10"/>
+      <c r="G423" s="5"/>
       <c r="H423" s="5">
         <v>788.0</v>
       </c>
@@ -66979,7 +66979,7 @@
         <v>9.5</v>
       </c>
       <c r="F424" s="6"/>
-      <c r="G424" s="10"/>
+      <c r="G424" s="5"/>
       <c r="H424" s="5">
         <v>1778.0</v>
       </c>
@@ -67110,10 +67110,596 @@
         <v>4.290852558737416</v>
       </c>
     </row>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <customSheetViews>
+    <customSheetView guid="{9BC4FBD6-2D2B-40A0-8F60-4009531500E2}" filter="1" showAutoFilter="1">
+      <autoFilter ref="$A$1:$AW$424"/>
+      <extLst>
+        <ext uri="GoogleSheetsCustomDataVersion1">
+          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="1613176250"/>
+        </ext>
+      </extLst>
+    </customSheetView>
+  </customSheetViews>
   <dataValidations>
     <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F424 K2:L424 N2:N424 P2:AW424">
-      <formula1>AND(ISNUMBER(F2),(NOT(OR(NOT(ISERROR(DATEVALUE(F2))), AND(ISNUMBER(F2), LEFT(CELL("format", F2))="D")))))</formula1>
+      <formula1/>
     </dataValidation>
   </dataValidations>
   <printOptions/>

--- a/xpts_playground.xlsx
+++ b/xpts_playground.xlsx
@@ -6,11 +6,11 @@
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="Z_9BC4FBD6_2D2B_40A0_8F60_4009531500E2_.wvu.FilterData">Sheet1!$A$1:$AW$424</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_ABBC3A64_2AEF_41C3_8E31_D2DBD81CF275_.wvu.FilterData">Sheet1!$A$1:$AW$424</definedName>
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{9BC4FBD6-2D2B-40A0-8F60-4009531500E2}" name="Table1 filter view"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{ABBC3A64-2AEF-41C3-8E31-D2DBD81CF275}" name="Table1 filter view"/>
   </customWorkbookViews>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -11356,124 +11356,124 @@
         <v>0</v>
       </c>
       <c r="K55" s="7">
-        <v>0.0</v>
+        <v>22.95</v>
       </c>
       <c r="L55" s="8">
         <v>0.06188335504567805</v>
       </c>
       <c r="M55" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.08792289</v>
       </c>
       <c r="N55" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>36.98937825</v>
       </c>
       <c r="O55" s="9">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.725341501</v>
       </c>
       <c r="P55" s="9">
-        <v>0.0</v>
+        <v>1.100080579179712</v>
       </c>
       <c r="Q55" s="9">
-        <v>0.0</v>
+        <v>1.074626170551621</v>
       </c>
       <c r="R55" s="9">
-        <v>0.0</v>
+        <v>1.08693288423758</v>
       </c>
       <c r="S55" s="9">
-        <v>0.0</v>
+        <v>1.111299196812562</v>
       </c>
       <c r="T55" s="9">
-        <v>0.0</v>
+        <v>1.0783690411486</v>
       </c>
       <c r="U55" s="9">
-        <v>0.0</v>
+        <v>1.105543768357467</v>
       </c>
       <c r="V55" s="9">
-        <v>0.0</v>
+        <v>1.106291135071231</v>
       </c>
       <c r="W55" s="9">
-        <v>0.0</v>
+        <v>1.068126743961954</v>
       </c>
       <c r="X55" s="9">
-        <v>0.0</v>
+        <v>1.086510521658208</v>
       </c>
       <c r="Y55" s="9">
-        <v>0.0</v>
+        <v>1.077222973600212</v>
       </c>
       <c r="Z55" s="9">
-        <v>0.0</v>
+        <v>1.074499408898079</v>
       </c>
       <c r="AA55" s="9">
-        <v>0.0</v>
+        <v>1.089338168821474</v>
       </c>
       <c r="AB55" s="9">
-        <v>0.0</v>
+        <v>1.08139601912339</v>
       </c>
       <c r="AC55" s="9">
-        <v>0.0</v>
+        <v>1.089573603641962</v>
       </c>
       <c r="AD55" s="9">
-        <v>0.0</v>
+        <v>1.080804824460545</v>
       </c>
       <c r="AE55" s="9">
-        <v>0.0</v>
+        <v>1.091332686128422</v>
       </c>
       <c r="AF55" s="9">
-        <v>0.0</v>
+        <v>1.084748252856239</v>
       </c>
       <c r="AG55" s="9">
-        <v>0.0</v>
+        <v>1.092788731259738</v>
       </c>
       <c r="AH55" s="9">
-        <v>0.0</v>
+        <v>1.092276203534172</v>
       </c>
       <c r="AI55" s="9">
-        <v>0.0</v>
+        <v>1.087806961770519</v>
       </c>
       <c r="AJ55" s="9">
-        <v>0.0</v>
+        <v>1.079156209829493</v>
       </c>
       <c r="AK55" s="9">
-        <v>0.0</v>
+        <v>1.075776587057506</v>
       </c>
       <c r="AL55" s="9">
-        <v>0.0</v>
+        <v>1.104187226373508</v>
       </c>
       <c r="AM55" s="9">
-        <v>0.0</v>
+        <v>1.077275094806508</v>
       </c>
       <c r="AN55" s="9">
-        <v>0.0</v>
+        <v>1.066674277512985</v>
       </c>
       <c r="AO55" s="9">
-        <v>0.0</v>
+        <v>1.096817646000076</v>
       </c>
       <c r="AP55" s="9">
-        <v>0.0</v>
+        <v>1.101279476912562</v>
       </c>
       <c r="AQ55" s="9">
-        <v>0.0</v>
+        <v>1.069365370366019</v>
       </c>
       <c r="AR55" s="9">
-        <v>0.0</v>
+        <v>1.087952072523251</v>
       </c>
       <c r="AS55" s="9">
-        <v>0.0</v>
+        <v>1.103625060795836</v>
       </c>
       <c r="AT55" s="9">
-        <v>0.0</v>
+        <v>1.088513579213627</v>
       </c>
       <c r="AU55" s="9">
-        <v>0.0</v>
+        <v>1.087638241714173</v>
       </c>
       <c r="AV55" s="9">
-        <v>0.0</v>
+        <v>1.107702030056263</v>
       </c>
       <c r="AW55" s="9">
-        <v>0.0</v>
+        <v>1.083847504822276</v>
       </c>
     </row>
     <row r="56" ht="15.0" customHeight="1">
@@ -53902,124 +53902,124 @@
         <v>0</v>
       </c>
       <c r="K337" s="7">
-        <v>0.0</v>
+        <v>22.95</v>
       </c>
       <c r="L337" s="8">
         <v>0.07888018793711915</v>
       </c>
       <c r="M337" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6211105</v>
       </c>
       <c r="N337" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>55.117757</v>
       </c>
       <c r="O337" s="9">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10.02141036</v>
       </c>
       <c r="P337" s="9">
-        <v>0.0</v>
+        <v>1.523206140823932</v>
       </c>
       <c r="Q337" s="9">
-        <v>0.0</v>
+        <v>1.636107095827404</v>
       </c>
       <c r="R337" s="9">
-        <v>0.0</v>
+        <v>1.627581432163388</v>
       </c>
       <c r="S337" s="9">
-        <v>0.0</v>
+        <v>1.590676705704119</v>
       </c>
       <c r="T337" s="9">
-        <v>0.0</v>
+        <v>1.867624559361957</v>
       </c>
       <c r="U337" s="9">
-        <v>0.0</v>
+        <v>1.405075170426845</v>
       </c>
       <c r="V337" s="9">
-        <v>0.0</v>
+        <v>1.68768876680528</v>
       </c>
       <c r="W337" s="9">
-        <v>0.0</v>
+        <v>1.681504884636411</v>
       </c>
       <c r="X337" s="9">
-        <v>0.0</v>
+        <v>1.841584141704126</v>
       </c>
       <c r="Y337" s="9">
-        <v>0.0</v>
+        <v>1.625545747270801</v>
       </c>
       <c r="Z337" s="9">
-        <v>0.0</v>
+        <v>1.482429441428507</v>
       </c>
       <c r="AA337" s="9">
-        <v>0.0</v>
+        <v>1.579808767389712</v>
       </c>
       <c r="AB337" s="9">
-        <v>0.0</v>
+        <v>1.583517951212852</v>
       </c>
       <c r="AC337" s="9">
-        <v>0.0</v>
+        <v>1.611939287370774</v>
       </c>
       <c r="AD337" s="9">
-        <v>0.0</v>
+        <v>1.670120914227784</v>
       </c>
       <c r="AE337" s="9">
-        <v>0.0</v>
+        <v>1.372605900417502</v>
       </c>
       <c r="AF337" s="9">
-        <v>0.0</v>
+        <v>1.617035285680901</v>
       </c>
       <c r="AG337" s="9">
-        <v>0.0</v>
+        <v>1.79013350886289</v>
       </c>
       <c r="AH337" s="9">
-        <v>0.0</v>
+        <v>1.513708589517228</v>
       </c>
       <c r="AI337" s="9">
-        <v>0.0</v>
+        <v>1.646056147787425</v>
       </c>
       <c r="AJ337" s="9">
-        <v>0.0</v>
+        <v>1.850601464015328</v>
       </c>
       <c r="AK337" s="9">
-        <v>0.0</v>
+        <v>1.62933225997538</v>
       </c>
       <c r="AL337" s="9">
-        <v>0.0</v>
+        <v>1.500509624971264</v>
       </c>
       <c r="AM337" s="9">
-        <v>0.0</v>
+        <v>1.543097432771227</v>
       </c>
       <c r="AN337" s="9">
-        <v>0.0</v>
+        <v>1.818434054624336</v>
       </c>
       <c r="AO337" s="9">
-        <v>0.0</v>
+        <v>1.43544365100733</v>
       </c>
       <c r="AP337" s="9">
-        <v>0.0</v>
+        <v>1.468549138446525</v>
       </c>
       <c r="AQ337" s="9">
-        <v>0.0</v>
+        <v>1.775668257633225</v>
       </c>
       <c r="AR337" s="9">
-        <v>0.0</v>
+        <v>1.911026026742467</v>
       </c>
       <c r="AS337" s="9">
-        <v>0.0</v>
+        <v>1.390130574550506</v>
       </c>
       <c r="AT337" s="9">
-        <v>0.0</v>
+        <v>1.499880758702847</v>
       </c>
       <c r="AU337" s="9">
-        <v>0.0</v>
+        <v>1.648896776919705</v>
       </c>
       <c r="AV337" s="9">
-        <v>0.0</v>
+        <v>1.467019700935281</v>
       </c>
       <c r="AW337" s="9">
-        <v>0.0</v>
+        <v>1.825216840253898</v>
       </c>
     </row>
     <row r="338" ht="15.0" customHeight="1">
@@ -54946,124 +54946,124 @@
         <v>0</v>
       </c>
       <c r="K344" s="7">
-        <v>0.0</v>
+        <v>23.98</v>
       </c>
       <c r="L344" s="8">
         <v>0.2142688969421128</v>
       </c>
       <c r="M344" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.019290564</v>
       </c>
       <c r="N344" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>68.65587918</v>
       </c>
       <c r="O344" s="9">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>15.25686204</v>
       </c>
       <c r="P344" s="9">
-        <v>0.0</v>
+        <v>1.85014112892637</v>
       </c>
       <c r="Q344" s="9">
-        <v>0.0</v>
+        <v>2.197822961398065</v>
       </c>
       <c r="R344" s="9">
         <v>0.0</v>
       </c>
       <c r="S344" s="9">
-        <v>0.0</v>
+        <v>2.034512036866793</v>
       </c>
       <c r="T344" s="9">
-        <v>0.0</v>
+        <v>3.980475607441037</v>
       </c>
       <c r="U344" s="9">
-        <v>0.0</v>
+        <v>1.869603545326194</v>
       </c>
       <c r="V344" s="9">
-        <v>0.0</v>
+        <v>1.754198672657453</v>
       </c>
       <c r="W344" s="9">
-        <v>0.0</v>
+        <v>2.255873856385713</v>
       </c>
       <c r="X344" s="9">
-        <v>0.0</v>
+        <v>1.883608075580522</v>
       </c>
       <c r="Y344" s="9">
-        <v>0.0</v>
+        <v>2.117026087797967</v>
       </c>
       <c r="Z344" s="9">
-        <v>0.0</v>
+        <v>2.037513738015424</v>
       </c>
       <c r="AA344" s="9">
-        <v>0.0</v>
+        <v>2.021963011021581</v>
       </c>
       <c r="AB344" s="9">
-        <v>0.0</v>
+        <v>2.391467207561101</v>
       </c>
       <c r="AC344" s="9">
-        <v>0.0</v>
+        <v>1.983096200111552</v>
       </c>
       <c r="AD344" s="9">
-        <v>0.0</v>
+        <v>2.064755466492776</v>
       </c>
       <c r="AE344" s="9">
-        <v>0.0</v>
+        <v>1.709419098287879</v>
       </c>
       <c r="AF344" s="9">
-        <v>0.0</v>
+        <v>2.353069540083693</v>
       </c>
       <c r="AG344" s="9">
-        <v>0.0</v>
+        <v>1.967070977818848</v>
       </c>
       <c r="AH344" s="9">
-        <v>0.0</v>
+        <v>2.100239954946075</v>
       </c>
       <c r="AI344" s="9">
-        <v>0.0</v>
+        <v>1.800758857724948</v>
       </c>
       <c r="AJ344" s="9">
-        <v>0.0</v>
+        <v>1.923456557591701</v>
       </c>
       <c r="AK344" s="9">
-        <v>0.0</v>
+        <v>2.126144476541179</v>
       </c>
       <c r="AL344" s="9">
-        <v>0.0</v>
+        <v>1.687382676653477</v>
       </c>
       <c r="AM344" s="9">
-        <v>0.0</v>
+        <v>2.455464457313631</v>
       </c>
       <c r="AN344" s="9">
-        <v>0.0</v>
+        <v>1.82348115423904</v>
       </c>
       <c r="AO344" s="9">
-        <v>0.0</v>
+        <v>1.912938604142862</v>
       </c>
       <c r="AP344" s="9">
-        <v>0.0</v>
+        <v>2.328935280532009</v>
       </c>
       <c r="AQ344" s="9">
-        <v>0.0</v>
+        <v>2.014448751797755</v>
       </c>
       <c r="AR344" s="9">
-        <v>0.0</v>
+        <v>1.849213839733865</v>
       </c>
       <c r="AS344" s="9">
-        <v>0.0</v>
+        <v>2.068944091048693</v>
       </c>
       <c r="AT344" s="9">
-        <v>0.0</v>
+        <v>1.972540322010057</v>
       </c>
       <c r="AU344" s="9">
-        <v>0.0</v>
+        <v>2.040095405675999</v>
       </c>
       <c r="AV344" s="9">
-        <v>0.0</v>
+        <v>1.803014076276197</v>
       </c>
       <c r="AW344" s="9">
-        <v>0.0</v>
+        <v>2.277203464612133</v>
       </c>
     </row>
     <row r="345" ht="15.0" customHeight="1">
@@ -67688,7 +67688,7 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{9BC4FBD6-2D2B-40A0-8F60-4009531500E2}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{ABBC3A64-2AEF-41C3-8E31-D2DBD81CF275}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$AW$424"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">

--- a/xpts_playground.xlsx
+++ b/xpts_playground.xlsx
@@ -6,15 +6,16 @@
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="Z_ABBC3A64_2AEF_41C3_8E31_D2DBD81CF275_.wvu.FilterData">Sheet1!$A$1:$AW$424</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet1!$A$1:$AW$424</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_F15D800C_13F5_4FDD_934F_17DEAE39F8DF_.wvu.FilterData">Sheet1!$A$1:$AW$424</definedName>
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{ABBC3A64-2AEF-41C3-8E31-D2DBD81CF275}" name="Table1 filter view"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{F15D800C-13F5-4FDD-934F-17DEAE39F8DF}" name="Table1 filter view"/>
   </customWorkbookViews>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="wo0TBAhA9t59iBAG8xui+3EBZKqmMNfnTFoFs2y7Bds="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="pEQ7wn3SeStoqmHCD3U6aH8+hc6PFxXfQ48dMrwqRyw="/>
     </ext>
   </extLst>
 </workbook>
@@ -2778,7 +2779,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2807,6 +2808,9 @@
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -2885,6 +2889,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AW424" displayName="Table1" name="Table1" id="1">
+  <autoFilter ref="$A$1:$AW$424"/>
   <tableColumns count="49">
     <tableColumn name="player_id" id="1"/>
     <tableColumn name="name" id="2"/>
@@ -3468,7 +3473,7 @@
       <c r="C3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E3" s="5">
@@ -3920,7 +3925,7 @@
       <c r="C6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E6" s="5">
@@ -4072,7 +4077,7 @@
       <c r="C7" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E7" s="5">
@@ -4528,7 +4533,7 @@
       <c r="C10" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E10" s="5">
@@ -6040,7 +6045,7 @@
       <c r="C20" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E20" s="5">
@@ -6944,7 +6949,7 @@
       <c r="C26" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E26" s="5">
@@ -7400,7 +7405,7 @@
       <c r="C29" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E29" s="5">
@@ -7852,7 +7857,7 @@
       <c r="C32" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E32" s="5">
@@ -8308,7 +8313,7 @@
       <c r="C35" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E35" s="5">
@@ -8912,7 +8917,7 @@
       <c r="C39" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E39" s="5">
@@ -9364,7 +9369,7 @@
       <c r="C42" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E42" s="5">
@@ -9816,7 +9821,7 @@
       <c r="C45" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D45" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E45" s="5">
@@ -11486,7 +11491,7 @@
       <c r="C56" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E56" s="5">
@@ -11638,7 +11643,7 @@
       <c r="C57" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D57" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E57" s="5">
@@ -12090,7 +12095,7 @@
       <c r="C60" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D60" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E60" s="5">
@@ -12546,7 +12551,7 @@
       <c r="C63" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D63" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E63" s="5">
@@ -15430,7 +15435,7 @@
       <c r="C82" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="D82" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E82" s="5">
@@ -19522,7 +19527,7 @@
       <c r="C109" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D109" s="5" t="s">
+      <c r="D109" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E109" s="5">
@@ -24824,7 +24829,7 @@
       <c r="C144" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D144" s="5" t="s">
+      <c r="D144" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E144" s="5">
@@ -26492,7 +26497,7 @@
       <c r="C155" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D155" s="5" t="s">
+      <c r="D155" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E155" s="5">
@@ -31026,7 +31031,7 @@
       <c r="C185" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D185" s="5" t="s">
+      <c r="D185" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E185" s="5">
@@ -31782,7 +31787,7 @@
       <c r="C190" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D190" s="5" t="s">
+      <c r="D190" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E190" s="5">
@@ -32390,7 +32395,7 @@
       <c r="C194" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D194" s="5" t="s">
+      <c r="D194" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E194" s="5">
@@ -34362,7 +34367,7 @@
       <c r="C207" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D207" s="5" t="s">
+      <c r="D207" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E207" s="5">
@@ -36148,7 +36153,7 @@
       <c r="C219" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D219" s="5" t="s">
+      <c r="D219" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E219" s="5">
@@ -36300,7 +36305,7 @@
       <c r="C220" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D220" s="5" t="s">
+      <c r="D220" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E220" s="5">
@@ -37810,7 +37815,7 @@
       <c r="C230" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D230" s="5" t="s">
+      <c r="D230" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E230" s="5">
@@ -38564,7 +38569,7 @@
       <c r="C235" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D235" s="5" t="s">
+      <c r="D235" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E235" s="5">
@@ -39908,7 +39913,7 @@
       <c r="C244" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D244" s="5" t="s">
+      <c r="D244" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E244" s="5">
@@ -42156,7 +42161,7 @@
       <c r="C259" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D259" s="5" t="s">
+      <c r="D259" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E259" s="5">
@@ -42308,7 +42313,7 @@
       <c r="C260" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D260" s="5" t="s">
+      <c r="D260" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E260" s="5">
@@ -43962,7 +43967,7 @@
       <c r="C271" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D271" s="5" t="s">
+      <c r="D271" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E271" s="5">
@@ -44110,7 +44115,7 @@
       <c r="C272" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D272" s="5" t="s">
+      <c r="D272" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E272" s="5">
@@ -45154,7 +45159,7 @@
       <c r="C279" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D279" s="5" t="s">
+      <c r="D279" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E279" s="5">
@@ -45302,7 +45307,7 @@
       <c r="C280" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D280" s="5" t="s">
+      <c r="D280" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E280" s="5">
@@ -46962,7 +46967,7 @@
       <c r="C291" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D291" s="5" t="s">
+      <c r="D291" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E291" s="5">
@@ -47114,7 +47119,7 @@
       <c r="C292" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D292" s="5" t="s">
+      <c r="D292" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E292" s="5">
@@ -51166,7 +51171,7 @@
       <c r="C319" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D319" s="5" t="s">
+      <c r="D319" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E319" s="5">
@@ -54032,7 +54037,7 @@
       <c r="C338" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D338" s="5" t="s">
+      <c r="D338" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E338" s="5">
@@ -54926,7 +54931,7 @@
       <c r="C344" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D344" s="5" t="s">
+      <c r="D344" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E344" s="5">
@@ -59596,7 +59601,7 @@
       <c r="C375" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="D375" s="5" t="s">
+      <c r="D375" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E375" s="5">
@@ -59748,7 +59753,7 @@
       <c r="C376" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="D376" s="5" t="s">
+      <c r="D376" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E376" s="5">
@@ -59900,7 +59905,7 @@
       <c r="C377" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="D377" s="5" t="s">
+      <c r="D377" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E377" s="5">
@@ -60048,7 +60053,7 @@
       <c r="C378" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="D378" s="5" t="s">
+      <c r="D378" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E378" s="5">
@@ -62312,7 +62317,7 @@
       <c r="C393" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="D393" s="5" t="s">
+      <c r="D393" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E393" s="5">
@@ -62460,7 +62465,7 @@
       <c r="C394" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="D394" s="5" t="s">
+      <c r="D394" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E394" s="5">
@@ -65036,7 +65041,7 @@
       <c r="C411" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D411" s="5" t="s">
+      <c r="D411" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E411" s="5">
@@ -65188,7 +65193,7 @@
       <c r="C412" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D412" s="5" t="s">
+      <c r="D412" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E412" s="5">
@@ -65340,7 +65345,7 @@
       <c r="C413" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D413" s="5" t="s">
+      <c r="D413" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E413" s="5">
@@ -65492,7 +65497,7 @@
       <c r="C414" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D414" s="5" t="s">
+      <c r="D414" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E414" s="5">
@@ -65800,130 +65805,130 @@
         <v>548.0</v>
       </c>
       <c r="I416" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J416" s="5" t="b">
         <v>0</v>
       </c>
       <c r="K416" s="7">
-        <v>22.95</v>
+        <v>74.05</v>
       </c>
       <c r="L416" s="8">
         <v>0.03799519891383461</v>
       </c>
       <c r="M416" s="9">
         <f t="shared" si="1"/>
-        <v>1.037995199</v>
+        <v>2.275810903</v>
       </c>
       <c r="N416" s="7">
         <f t="shared" si="2"/>
-        <v>35.29183676</v>
+        <v>77.37757071</v>
       </c>
       <c r="O416" s="9">
         <f t="shared" si="3"/>
-        <v>5.041690966</v>
+        <v>11.05393867</v>
       </c>
       <c r="P416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.308745724016267</v>
       </c>
       <c r="Q416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.330993706180508</v>
       </c>
       <c r="R416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.367569593121218</v>
       </c>
       <c r="S416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.273217860689495</v>
       </c>
       <c r="T416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.225820862799466</v>
       </c>
       <c r="U416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.330435892573647</v>
       </c>
       <c r="V416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.372110692179604</v>
       </c>
       <c r="W416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.185315132741618</v>
       </c>
       <c r="X416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.384573188825561</v>
       </c>
       <c r="Y416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.256611572687496</v>
       </c>
       <c r="Z416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.176060972933004</v>
       </c>
       <c r="AA416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.204684552654252</v>
       </c>
       <c r="AB416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.185981456031371</v>
       </c>
       <c r="AC416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.249538569367154</v>
       </c>
       <c r="AD416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.255115005142205</v>
       </c>
       <c r="AE416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.172712808004509</v>
       </c>
       <c r="AF416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.43682084567227</v>
       </c>
       <c r="AG416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.438871937499296</v>
       </c>
       <c r="AH416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.21076674654705</v>
       </c>
       <c r="AI416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.439443530453098</v>
       </c>
       <c r="AJ416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.167468363449975</v>
       </c>
       <c r="AK416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.143381188314537</v>
       </c>
       <c r="AL416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.35894472495805</v>
       </c>
       <c r="AM416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.263126848631771</v>
       </c>
       <c r="AN416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.278667608988138</v>
       </c>
       <c r="AO416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.262975294050843</v>
       </c>
       <c r="AP416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.278541060536541</v>
       </c>
       <c r="AQ416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.26714095259445</v>
       </c>
       <c r="AR416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.267254562297615</v>
       </c>
       <c r="AS416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.1618319241121</v>
       </c>
       <c r="AT416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.378699506796937</v>
       </c>
       <c r="AU416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.328436386555135</v>
       </c>
       <c r="AV416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.114080417111447</v>
       </c>
       <c r="AW416" s="9">
-        <v>1.03799519889702</v>
+        <v>2.301631221284787</v>
       </c>
     </row>
     <row r="417" ht="15.0" customHeight="1">
@@ -66380,7 +66385,7 @@
       <c r="C420" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D420" s="5" t="s">
+      <c r="D420" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E420" s="5">
@@ -66528,7 +66533,7 @@
       <c r="C421" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D421" s="5" t="s">
+      <c r="D421" s="10" t="s">
         <v>56</v>
       </c>
       <c r="E421" s="5">
@@ -67688,7 +67693,7 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{ABBC3A64-2AEF-41C3-8E31-D2DBD81CF275}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{F15D800C-13F5-4FDD-934F-17DEAE39F8DF}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$AW$424"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">

--- a/xpts_playground.xlsx
+++ b/xpts_playground.xlsx
@@ -7,11 +7,11 @@
   </sheets>
   <definedNames>
     <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet1!$A$1:$AW$424</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_F15D800C_13F5_4FDD_934F_17DEAE39F8DF_.wvu.FilterData">Sheet1!$A$1:$AW$424</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_A64A7C44_8EA4_4FE7_8AB9_3FB57CBA6668_.wvu.FilterData">Sheet1!$A$1:$AW$424</definedName>
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{F15D800C-13F5-4FDD-934F-17DEAE39F8DF}" name="Table1 filter view"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{A64A7C44-8EA4-4FE7-8AB9-3FB57CBA6668}" name="Table1 filter view"/>
   </customWorkbookViews>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -192,7 +192,7 @@
     <t>FEY</t>
   </si>
   <si>
-    <t>ATT</t>
+    <t>FWD</t>
   </si>
   <si>
     <t>Godts_AJA</t>
@@ -2811,7 +2811,7 @@
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -67693,7 +67693,7 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{F15D800C-13F5-4FDD-934F-17DEAE39F8DF}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{A64A7C44-8EA4-4FE7-8AB9-3FB57CBA6668}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$AW$424"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
